--- a/Pravartiya/data/temp/Searching_agent_output_mac.xlsx
+++ b/Pravartiya/data/temp/Searching_agent_output_mac.xlsx
@@ -58,7 +58,7 @@
     <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015 [Last amended on January 22, 2026]</t>
   </si>
   <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1777351317428.pdf</t>
+    <t>file:///Users/admin/Downloads/1780915347745.pdf</t>
   </si>
   <si>
     <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
@@ -339,7 +339,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,12 +364,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -416,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -434,18 +428,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -762,15 +744,15 @@
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="11" width="114.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="114.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -1034,14 +1016,14 @@
         <v>50</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="4">
         <v>2026</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -1053,7 +1035,7 @@
       <c r="F10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="5" t="s">
         <v>54</v>
       </c>
       <c r="H10" s="3" t="s">
@@ -1063,14 +1045,14 @@
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="4">
         <v>2026</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -1082,7 +1064,7 @@
       <c r="F11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="5" t="s">
         <v>59</v>
       </c>
       <c r="H11" s="3" t="s">
@@ -1092,14 +1074,14 @@
         <v>61</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="4">
         <v>2026</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -1111,7 +1093,7 @@
       <c r="F12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="5" t="s">
         <v>63</v>
       </c>
       <c r="H12" s="3" t="s">
@@ -1121,14 +1103,14 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="4">
         <v>2026</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -1140,7 +1122,7 @@
       <c r="F13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="5" t="s">
         <v>68</v>
       </c>
       <c r="H13" s="3" t="s">
@@ -1150,14 +1132,14 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="4">
         <v>2026</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -1169,7 +1151,7 @@
       <c r="F14" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H14" s="3" t="s">
@@ -1179,14 +1161,14 @@
         <v>75</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="4">
         <v>2026</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -1198,7 +1180,7 @@
       <c r="F15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="5" t="s">
         <v>80</v>
       </c>
       <c r="H15" s="3" t="s">
@@ -1208,14 +1190,14 @@
         <v>82</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="4">
         <v>2026</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -1227,7 +1209,7 @@
       <c r="F16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="5" t="s">
         <v>85</v>
       </c>
       <c r="H16" s="3" t="s">
@@ -1244,7 +1226,7 @@
       <c r="B17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="4">
         <v>2026</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -1256,7 +1238,7 @@
       <c r="F17" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="5" t="s">
         <v>90</v>
       </c>
       <c r="H17" s="3" t="s">
@@ -1273,7 +1255,7 @@
       <c r="B18" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="4">
         <v>2026</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -1285,7 +1267,7 @@
       <c r="F18" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="5" t="s">
         <v>94</v>
       </c>
       <c r="H18" s="3" t="s">
@@ -1302,7 +1284,7 @@
       <c r="B19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="4">
         <v>2026</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -1314,7 +1296,7 @@
       <c r="F19" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="5" t="s">
         <v>98</v>
       </c>
       <c r="H19" s="3" t="s">
@@ -1331,7 +1313,7 @@
       <c r="B20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="4">
         <v>2026</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -1343,7 +1325,7 @@
       <c r="F20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="5" t="s">
         <v>103</v>
       </c>
       <c r="H20" s="3" t="s">
@@ -1356,11 +1338,11 @@
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
-      <c r="C21" s="7"/>
+      <c r="C21" s="4"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="8"/>
+      <c r="G21" s="5"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
